--- a/SensitivityAnalysis/SingleSNP/MR_dat_continuous.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_continuous.xlsx
@@ -6,23 +6,23 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="3148-0.0" r:id="rId3" sheetId="1"/>
-    <sheet name="30690-0.0" r:id="rId4" sheetId="2"/>
-    <sheet name="30780-0.0" r:id="rId5" sheetId="3"/>
-    <sheet name="30760-0.0" r:id="rId6" sheetId="4"/>
-    <sheet name="30870-0.0" r:id="rId7" sheetId="5"/>
-    <sheet name="30630-0.0" r:id="rId8" sheetId="6"/>
-    <sheet name="30640-0.0" r:id="rId9" sheetId="7"/>
-    <sheet name="30710-0.0" r:id="rId10" sheetId="8"/>
-    <sheet name="30790-0.0" r:id="rId11" sheetId="9"/>
-    <sheet name="30750-0.0" r:id="rId12" sheetId="10"/>
-    <sheet name="30740-0.0" r:id="rId13" sheetId="11"/>
+    <sheet name="eBMD" r:id="rId3" sheetId="1"/>
+    <sheet name="Cholesterol" r:id="rId4" sheetId="2"/>
+    <sheet name="LDL" r:id="rId5" sheetId="3"/>
+    <sheet name="HDL" r:id="rId6" sheetId="4"/>
+    <sheet name="Triglycerides" r:id="rId7" sheetId="5"/>
+    <sheet name="Apo-A" r:id="rId8" sheetId="6"/>
+    <sheet name="Apo-B" r:id="rId9" sheetId="7"/>
+    <sheet name="CRP" r:id="rId10" sheetId="8"/>
+    <sheet name="Lipoprotein" r:id="rId11" sheetId="9"/>
+    <sheet name="HbA1c" r:id="rId12" sheetId="10"/>
+    <sheet name="Glucose" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="53">
   <si>
     <t>SNP</t>
   </si>
@@ -75,12 +75,39 @@
     <t>outcome</t>
   </si>
   <si>
+    <t>beta_95L</t>
+  </si>
+  <si>
+    <t>beta_95U</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
     <t>pval.exposure</t>
   </si>
   <si>
+    <t>X_.log10_p.value</t>
+  </si>
+  <si>
+    <t>q_statistic</t>
+  </si>
+  <si>
+    <t>q_p.value</t>
+  </si>
+  <si>
+    <t>i2</t>
+  </si>
+  <si>
+    <t>n_studies</t>
+  </si>
+  <si>
     <t>N.exposure</t>
   </si>
   <si>
+    <t>effects</t>
+  </si>
+  <si>
     <t>se.exposure</t>
   </si>
   <si>
@@ -90,9 +117,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -117,7 +141,10 @@
     <t>FALSE</t>
   </si>
   <si>
-    <t>3148-0.0</t>
+    <t>eBMD</t>
+  </si>
+  <si>
+    <t>+++</t>
   </si>
   <si>
     <t>Sclerostin</t>
@@ -126,34 +153,34 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>30690-0.0</t>
-  </si>
-  <si>
-    <t>30780-0.0</t>
-  </si>
-  <si>
-    <t>30760-0.0</t>
-  </si>
-  <si>
-    <t>30870-0.0</t>
-  </si>
-  <si>
-    <t>30630-0.0</t>
-  </si>
-  <si>
-    <t>30640-0.0</t>
-  </si>
-  <si>
-    <t>30710-0.0</t>
-  </si>
-  <si>
-    <t>30790-0.0</t>
-  </si>
-  <si>
-    <t>30750-0.0</t>
-  </si>
-  <si>
-    <t>30740-0.0</t>
+    <t>Cholesterol</t>
+  </si>
+  <si>
+    <t>LDL</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>Triglycerides</t>
+  </si>
+  <si>
+    <t>Apo-A</t>
+  </si>
+  <si>
+    <t>Apo-B</t>
+  </si>
+  <si>
+    <t>CRP</t>
+  </si>
+  <si>
+    <t>Lipoprotein</t>
+  </si>
+  <si>
+    <t>HbA1c</t>
+  </si>
+  <si>
+    <t>Glucose</t>
   </si>
 </sst>
 </file>
@@ -281,25 +308,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -314,16 +365,16 @@
         <v>0.415977286618795</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O2" t="n">
         <v>0.0056440565000923934</v>
@@ -335,33 +386,57 @@
         <v>214323.0</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -455,25 +530,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -488,16 +587,16 @@
         <v>0.4160857451526696</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
         <v>0.004521483480922011</v>
@@ -509,33 +608,57 @@
         <v>351740.0</v>
       </c>
       <c r="R2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11E-9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>49372.0</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AH2" t="s">
         <v>42</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.11E-9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>49372.0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.00684234693877551</v>
-      </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -629,25 +752,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -662,16 +809,16 @@
         <v>0.4160912181690482</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="O2" t="n">
         <v>0.004733978556172183</v>
@@ -683,33 +830,57 @@
         <v>321778.0</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -803,25 +974,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -836,16 +1031,16 @@
         <v>0.41616132324636596</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O2" t="n">
         <v>0.004438654407112916</v>
@@ -857,33 +1052,57 @@
         <v>351741.0</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -977,25 +1196,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1010,16 +1253,16 @@
         <v>0.41617533965649833</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
         <v>0.004496342158307523</v>
@@ -1031,33 +1274,57 @@
         <v>351090.0</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1151,25 +1418,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1184,16 +1475,16 @@
         <v>0.416068594782101</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
         <v>0.004299114963588015</v>
@@ -1205,33 +1496,57 @@
         <v>322007.0</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1325,25 +1640,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1358,16 +1697,16 @@
         <v>0.4161777426220366</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
         <v>0.004425804551481263</v>
@@ -1379,33 +1718,57 @@
         <v>351452.0</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1499,25 +1862,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1532,16 +1919,16 @@
         <v>0.41605928313128854</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.004373662814238708</v>
@@ -1553,33 +1940,57 @@
         <v>320226.0</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1673,25 +2084,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1706,16 +2141,16 @@
         <v>0.4162064798493882</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
         <v>0.00451998730545515</v>
@@ -1727,33 +2162,57 @@
         <v>350039.0</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1847,25 +2306,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1880,16 +2363,16 @@
         <v>0.4161720920293468</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0.004516207786443735</v>
@@ -1901,33 +2384,57 @@
         <v>350975.0</v>
       </c>
       <c r="R2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11E-9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>49372.0</v>
+      </c>
+      <c r="AC2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.11E-9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>49372.0</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2021,25 +2528,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -2054,16 +2585,16 @@
         <v>0.4160906517605684</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
         <v>0.005060575174380083</v>
@@ -2075,33 +2606,57 @@
         <v>279796.0</v>
       </c>
       <c r="R2" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11E-9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>49372.0</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AE2" t="s">
         <v>41</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.11E-9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>49372.0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.00684234693877551</v>
-      </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/SensitivityAnalysis/SingleSNP/MR_dat_continuous.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_continuous.xlsx
@@ -353,16 +353,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04849768504033609</v>
+        <v>-0.04682543749102529</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.415977286618795</v>
+        <v>0.6011864688977204</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -377,13 +377,13 @@
         <v>39</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0056440565000923934</v>
+        <v>0.007046052315045322</v>
       </c>
       <c r="P2" t="n">
-        <v>8.550548359273012E-18</v>
+        <v>3.030439163737735E-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>214323.0</v>
+        <v>138141.0</v>
       </c>
       <c r="R2" t="s">
         <v>39</v>
@@ -575,16 +575,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.551722631445365E-4</v>
+        <v>-0.003660777914400295</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4160857451526696</v>
+        <v>0.60199228875205</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -599,13 +599,13 @@
         <v>51</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004521483480922011</v>
+        <v>0.005566912652613397</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9373888907659219</v>
+        <v>0.5107986027817576</v>
       </c>
       <c r="Q2" t="n">
-        <v>351740.0</v>
+        <v>231091.0</v>
       </c>
       <c r="R2" t="s">
         <v>51</v>
@@ -797,16 +797,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.004631981165334541</v>
+        <v>-0.011400852534722661</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4160912181690482</v>
+        <v>0.6018473872800674</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -821,13 +821,13 @@
         <v>52</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004733978556172183</v>
+        <v>0.005815807564149078</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3278504721819454</v>
+        <v>0.04995953668654066</v>
       </c>
       <c r="Q2" t="n">
-        <v>321778.0</v>
+        <v>211542.0</v>
       </c>
       <c r="R2" t="s">
         <v>52</v>
@@ -1019,16 +1019,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0031614816960992783</v>
+        <v>-0.005563097021752728</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41616132324636596</v>
+        <v>0.6018997003204366</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1043,13 +1043,13 @@
         <v>43</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004438654407112916</v>
+        <v>0.005477396730130087</v>
       </c>
       <c r="P2" t="n">
-        <v>0.47630346494143017</v>
+        <v>0.3097989720398852</v>
       </c>
       <c r="Q2" t="n">
-        <v>351741.0</v>
+        <v>231247.0</v>
       </c>
       <c r="R2" t="s">
         <v>43</v>
@@ -1241,16 +1241,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.004101141888513507</v>
+        <v>-0.006524545535169864</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41617533965649833</v>
+        <v>0.6019275511132485</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1265,13 +1265,13 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004496342158307523</v>
+        <v>0.00555014762802485</v>
       </c>
       <c r="P2" t="n">
-        <v>0.36171340270922425</v>
+        <v>0.23977095254547723</v>
       </c>
       <c r="Q2" t="n">
-        <v>351090.0</v>
+        <v>230811.0</v>
       </c>
       <c r="R2" t="s">
         <v>44</v>
@@ -1463,16 +1463,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.010396504791458061</v>
+        <v>0.007380849848315527</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.416068594782101</v>
+        <v>0.6018683862433862</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1487,13 +1487,13 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004299114963588015</v>
+        <v>0.005313876336351969</v>
       </c>
       <c r="P2" t="n">
-        <v>0.015594213886514784</v>
+        <v>0.16484132923230987</v>
       </c>
       <c r="Q2" t="n">
-        <v>322007.0</v>
+        <v>211680.0</v>
       </c>
       <c r="R2" t="s">
         <v>45</v>
@@ -1685,16 +1685,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01494086826170413</v>
+        <v>-0.01547700240491007</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161777426220366</v>
+        <v>0.6019087190806985</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1709,13 +1709,13 @@
         <v>46</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004425804551481263</v>
+        <v>0.005460710958549628</v>
       </c>
       <c r="P2" t="n">
-        <v>7.359502464391945E-4</v>
+        <v>0.004593782876831189</v>
       </c>
       <c r="Q2" t="n">
-        <v>351452.0</v>
+        <v>231045.0</v>
       </c>
       <c r="R2" t="s">
         <v>46</v>
@@ -1907,16 +1907,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007021690933490242</v>
+        <v>0.0028513059472051877</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41605928313128854</v>
+        <v>0.6019452757588714</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1931,13 +1931,13 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004373662814238708</v>
+        <v>0.005408874313332539</v>
       </c>
       <c r="P2" t="n">
-        <v>0.10839609774250065</v>
+        <v>0.5980876908786741</v>
       </c>
       <c r="Q2" t="n">
-        <v>320226.0</v>
+        <v>210510.0</v>
       </c>
       <c r="R2" t="s">
         <v>47</v>
@@ -2129,16 +2129,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.007410104487496083</v>
+        <v>-0.009041007452368148</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4162064798493882</v>
+        <v>0.6019512407109643</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -2153,13 +2153,13 @@
         <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00451998730545515</v>
+        <v>0.00558330109203913</v>
       </c>
       <c r="P2" t="n">
-        <v>0.10112916287179191</v>
+        <v>0.1053853339718759</v>
       </c>
       <c r="Q2" t="n">
-        <v>350039.0</v>
+        <v>230110.0</v>
       </c>
       <c r="R2" t="s">
         <v>48</v>
@@ -2351,16 +2351,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0017787381903987731</v>
+        <v>6.141563695543588E-4</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161720920293468</v>
+        <v>0.601931502515677</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -2375,13 +2375,13 @@
         <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004516207786443735</v>
+        <v>0.005575091449627981</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6936871619733798</v>
+        <v>0.912281969297668</v>
       </c>
       <c r="Q2" t="n">
-        <v>350975.0</v>
+        <v>230753.0</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
@@ -2573,16 +2573,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>3.616398040624297E-5</v>
+        <v>0.004020196535178995</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4160906517605684</v>
+        <v>0.6018455508070882</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -2597,13 +2597,13 @@
         <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005060575174380083</v>
+        <v>0.0062535128731321145</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9942981955107479</v>
+        <v>0.5203091854673492</v>
       </c>
       <c r="Q2" t="n">
-        <v>279796.0</v>
+        <v>183685.0</v>
       </c>
       <c r="R2" t="s">
         <v>50</v>
